--- a/annotated_data/mcmaster_reddit.xlsx
+++ b/annotated_data/mcmaster_reddit.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="1128">
   <si>
     <t>id</t>
   </si>
@@ -6357,6 +6357,9 @@
       <c r="B167" t="s">
         <v>168</v>
       </c>
+      <c r="C167" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
@@ -6521,6 +6524,9 @@
       <c r="B7" t="s">
         <v>188</v>
       </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
@@ -8244,6 +8250,9 @@
       </c>
       <c r="B164" t="s">
         <v>344</v>
+      </c>
+      <c r="C164" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -12232,6 +12241,9 @@
       <c r="B3" t="s">
         <v>529</v>
       </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
